--- a/data-raw/xlsx/tabla_etiquetas.xlsx
+++ b/data-raw/xlsx/tabla_etiquetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fernando_gallegos\Proyectos\odsa.eusilc\data-raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED2A23A-C1DF-46C0-8F77-F9771848E87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A217F-123A-45AF-BD81-CEB3BA3AB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$336</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$338</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1529" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="444">
   <si>
     <t>variable</t>
   </si>
@@ -1348,6 +1348,18 @@
   </si>
   <si>
     <t>Terciario incompleto o más</t>
+  </si>
+  <si>
+    <t>pi07</t>
+  </si>
+  <si>
+    <t>Urbanización</t>
+  </si>
+  <si>
+    <t>Urbano</t>
+  </si>
+  <si>
+    <t>Rural</t>
   </si>
 </sst>
 </file>
@@ -1587,7 +1599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F336"/>
+  <dimension ref="A1:F338"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -1701,35 +1713,47 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>20</v>
+        <v>440</v>
       </c>
       <c r="B8" t="s">
         <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>441</v>
+      </c>
+      <c r="E8" t="s">
+        <v>442</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>23</v>
+        <v>440</v>
       </c>
       <c r="B9" t="s">
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>441</v>
+      </c>
+      <c r="E9" t="s">
+        <v>443</v>
+      </c>
+      <c r="F9">
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
         <v>7</v>
@@ -1738,12 +1762,12 @@
         <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
         <v>7</v>
@@ -1752,18 +1776,12 @@
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
         <v>7</v>
@@ -1772,18 +1790,12 @@
         <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F12">
-        <v>2</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
         <v>7</v>
@@ -1792,10 +1804,10 @@
         <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E13" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F13">
         <v>1</v>
@@ -1803,7 +1815,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
         <v>7</v>
@@ -1812,10 +1824,10 @@
         <v>21</v>
       </c>
       <c r="D14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F14">
         <v>2</v>
@@ -1835,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1855,10 +1867,10 @@
         <v>32</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F16">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,15 +1887,15 @@
         <v>32</v>
       </c>
       <c r="E17" t="s">
-        <v>439</v>
+        <v>35</v>
       </c>
       <c r="F17">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -1892,18 +1904,18 @@
         <v>21</v>
       </c>
       <c r="D18" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F18">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s">
         <v>7</v>
@@ -1912,18 +1924,18 @@
         <v>21</v>
       </c>
       <c r="D19" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
-        <v>40</v>
+        <v>439</v>
       </c>
       <c r="F19">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
         <v>7</v>
@@ -1932,10 +1944,10 @@
         <v>21</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -1943,7 +1955,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
         <v>7</v>
@@ -1952,10 +1964,10 @@
         <v>21</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E21" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F21">
         <v>2</v>
@@ -1963,19 +1975,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
         <v>7</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -1983,19 +1995,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B23" t="s">
         <v>7</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D23" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="F23">
         <v>2</v>
@@ -2003,7 +2015,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
         <v>7</v>
@@ -2012,10 +2024,10 @@
         <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -2023,7 +2035,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
         <v>7</v>
@@ -2032,10 +2044,10 @@
         <v>46</v>
       </c>
       <c r="D25" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -2055,15 +2067,15 @@
         <v>51</v>
       </c>
       <c r="E26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F26">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
         <v>7</v>
@@ -2072,18 +2084,18 @@
         <v>46</v>
       </c>
       <c r="D27" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E27" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="F27">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
         <v>7</v>
@@ -2092,13 +2104,13 @@
         <v>46</v>
       </c>
       <c r="D28" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E28" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F28">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2115,10 +2127,10 @@
         <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F29">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2135,15 +2147,15 @@
         <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F30">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B31" t="s">
         <v>7</v>
@@ -2155,15 +2167,15 @@
         <v>56</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F31">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B32" t="s">
         <v>7</v>
@@ -2175,10 +2187,10 @@
         <v>56</v>
       </c>
       <c r="E32" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F32">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2195,10 +2207,10 @@
         <v>56</v>
       </c>
       <c r="E33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,15 +2227,15 @@
         <v>56</v>
       </c>
       <c r="E34" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F34">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B35" t="s">
         <v>7</v>
@@ -2235,15 +2247,15 @@
         <v>56</v>
       </c>
       <c r="E35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F35">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
         <v>7</v>
@@ -2255,10 +2267,10 @@
         <v>56</v>
       </c>
       <c r="E36" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F36">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2275,10 +2287,10 @@
         <v>56</v>
       </c>
       <c r="E37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F37">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2295,15 +2307,15 @@
         <v>56</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F38">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B39" t="s">
         <v>7</v>
@@ -2312,12 +2324,18 @@
         <v>46</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="E39" t="s">
+        <v>59</v>
+      </c>
+      <c r="F39">
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B40" t="s">
         <v>7</v>
@@ -2326,12 +2344,18 @@
         <v>46</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>56</v>
+      </c>
+      <c r="E40" t="s">
+        <v>60</v>
+      </c>
+      <c r="F40">
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
         <v>7</v>
@@ -2345,7 +2369,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -2354,18 +2378,12 @@
         <v>46</v>
       </c>
       <c r="D42" t="s">
-        <v>68</v>
-      </c>
-      <c r="E42" t="s">
-        <v>69</v>
-      </c>
-      <c r="F42">
-        <v>1</v>
+        <v>64</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B43" t="s">
         <v>7</v>
@@ -2374,13 +2392,7 @@
         <v>46</v>
       </c>
       <c r="D43" t="s">
-        <v>68</v>
-      </c>
-      <c r="E43" t="s">
-        <v>70</v>
-      </c>
-      <c r="F43">
-        <v>2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2397,10 +2409,10 @@
         <v>68</v>
       </c>
       <c r="E44" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F44">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2417,10 +2429,10 @@
         <v>68</v>
       </c>
       <c r="E45" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F45">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2437,10 +2449,10 @@
         <v>68</v>
       </c>
       <c r="E46" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F46">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2457,10 +2469,10 @@
         <v>68</v>
       </c>
       <c r="E47" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F47">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2477,10 +2489,10 @@
         <v>68</v>
       </c>
       <c r="E48" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F48">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2497,10 +2509,10 @@
         <v>68</v>
       </c>
       <c r="E49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F49">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2517,10 +2529,10 @@
         <v>68</v>
       </c>
       <c r="E50" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F50">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2537,15 +2549,15 @@
         <v>68</v>
       </c>
       <c r="E51" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F51">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B52" t="s">
         <v>7</v>
@@ -2557,15 +2569,15 @@
         <v>68</v>
       </c>
       <c r="E52" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B53" t="s">
         <v>7</v>
@@ -2577,10 +2589,10 @@
         <v>68</v>
       </c>
       <c r="E53" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F53">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2597,10 +2609,10 @@
         <v>68</v>
       </c>
       <c r="E54" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F54">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2617,10 +2629,10 @@
         <v>68</v>
       </c>
       <c r="E55" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F55">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2637,10 +2649,10 @@
         <v>68</v>
       </c>
       <c r="E56" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F56">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2657,10 +2669,10 @@
         <v>68</v>
       </c>
       <c r="E57" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F57">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2677,10 +2689,10 @@
         <v>68</v>
       </c>
       <c r="E58" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F58">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2697,10 +2709,10 @@
         <v>68</v>
       </c>
       <c r="E59" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F59">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2717,10 +2729,10 @@
         <v>68</v>
       </c>
       <c r="E60" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F60">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2737,15 +2749,15 @@
         <v>68</v>
       </c>
       <c r="E61" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F61">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
         <v>7</v>
@@ -2757,15 +2769,15 @@
         <v>68</v>
       </c>
       <c r="E62" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F62">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B63" t="s">
         <v>7</v>
@@ -2777,10 +2789,10 @@
         <v>68</v>
       </c>
       <c r="E63" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="F63">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -2797,10 +2809,10 @@
         <v>68</v>
       </c>
       <c r="E64" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F64">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -2817,10 +2829,10 @@
         <v>68</v>
       </c>
       <c r="E65" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F65">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -2837,10 +2849,10 @@
         <v>68</v>
       </c>
       <c r="E66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F66">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -2857,10 +2869,10 @@
         <v>68</v>
       </c>
       <c r="E67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F67">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -2877,10 +2889,10 @@
         <v>68</v>
       </c>
       <c r="E68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F68">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -2897,10 +2909,10 @@
         <v>68</v>
       </c>
       <c r="E69" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F69">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -2917,10 +2929,10 @@
         <v>68</v>
       </c>
       <c r="E70" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F70">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -2937,15 +2949,15 @@
         <v>68</v>
       </c>
       <c r="E71" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B72" t="s">
         <v>7</v>
@@ -2954,18 +2966,18 @@
         <v>46</v>
       </c>
       <c r="D72" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E72" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="F72">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B73" t="s">
         <v>7</v>
@@ -2974,13 +2986,13 @@
         <v>46</v>
       </c>
       <c r="D73" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="E73" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="F73">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -2997,10 +3009,10 @@
         <v>82</v>
       </c>
       <c r="E74" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F74">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3017,15 +3029,15 @@
         <v>82</v>
       </c>
       <c r="E75" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F75">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B76" t="s">
         <v>7</v>
@@ -3037,15 +3049,15 @@
         <v>82</v>
       </c>
       <c r="E76" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="B77" t="s">
         <v>7</v>
@@ -3057,10 +3069,10 @@
         <v>82</v>
       </c>
       <c r="E77" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F77">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3077,10 +3089,10 @@
         <v>82</v>
       </c>
       <c r="E78" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F78">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3097,15 +3109,15 @@
         <v>82</v>
       </c>
       <c r="E79" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F79">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B80" t="s">
         <v>7</v>
@@ -3117,15 +3129,15 @@
         <v>82</v>
       </c>
       <c r="E80" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F80">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B81" t="s">
         <v>7</v>
@@ -3137,10 +3149,10 @@
         <v>82</v>
       </c>
       <c r="E81" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F81">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3157,10 +3169,10 @@
         <v>82</v>
       </c>
       <c r="E82" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="F82">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3177,15 +3189,15 @@
         <v>82</v>
       </c>
       <c r="E83" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F83">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B84" t="s">
         <v>7</v>
@@ -3194,18 +3206,18 @@
         <v>46</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E84" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B85" t="s">
         <v>7</v>
@@ -3214,18 +3226,18 @@
         <v>46</v>
       </c>
       <c r="D85" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="E85" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="F85">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B86" t="s">
         <v>7</v>
@@ -3245,7 +3257,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B87" t="s">
         <v>7</v>
@@ -3265,7 +3277,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B88" t="s">
         <v>7</v>
@@ -3285,7 +3297,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B89" t="s">
         <v>7</v>
@@ -3305,7 +3317,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B90" t="s">
         <v>7</v>
@@ -3314,10 +3326,10 @@
         <v>46</v>
       </c>
       <c r="D90" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E90" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F90">
         <v>1</v>
@@ -3325,7 +3337,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B91" t="s">
         <v>7</v>
@@ -3334,10 +3346,10 @@
         <v>46</v>
       </c>
       <c r="D91" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E91" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F91">
         <v>2</v>
@@ -3357,10 +3369,10 @@
         <v>95</v>
       </c>
       <c r="E92" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F92">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3377,10 +3389,10 @@
         <v>95</v>
       </c>
       <c r="E93" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F93">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -3397,10 +3409,10 @@
         <v>95</v>
       </c>
       <c r="E94" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F94">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -3417,10 +3429,10 @@
         <v>95</v>
       </c>
       <c r="E95" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F95">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -3437,10 +3449,10 @@
         <v>95</v>
       </c>
       <c r="E96" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F96">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -3457,10 +3469,10 @@
         <v>95</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F97">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -3477,15 +3489,15 @@
         <v>95</v>
       </c>
       <c r="E98" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F98">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B99" t="s">
         <v>7</v>
@@ -3497,15 +3509,15 @@
         <v>95</v>
       </c>
       <c r="E99" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F99">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B100" t="s">
         <v>7</v>
@@ -3517,10 +3529,10 @@
         <v>95</v>
       </c>
       <c r="E100" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F100">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -3537,10 +3549,10 @@
         <v>95</v>
       </c>
       <c r="E101" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F101">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -3557,10 +3569,10 @@
         <v>95</v>
       </c>
       <c r="E102" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F102">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -3577,10 +3589,10 @@
         <v>95</v>
       </c>
       <c r="E103" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F103">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3597,10 +3609,10 @@
         <v>95</v>
       </c>
       <c r="E104" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F104">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3617,10 +3629,10 @@
         <v>95</v>
       </c>
       <c r="E105" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F105">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3637,10 +3649,10 @@
         <v>95</v>
       </c>
       <c r="E106" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F106">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3657,15 +3669,15 @@
         <v>95</v>
       </c>
       <c r="E107" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F107">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B108" t="s">
         <v>7</v>
@@ -3677,15 +3689,15 @@
         <v>95</v>
       </c>
       <c r="E108" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
         <v>7</v>
@@ -3697,10 +3709,10 @@
         <v>95</v>
       </c>
       <c r="E109" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F109">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3717,10 +3729,10 @@
         <v>95</v>
       </c>
       <c r="E110" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F110">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3737,10 +3749,10 @@
         <v>95</v>
       </c>
       <c r="E111" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F111">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3757,10 +3769,10 @@
         <v>95</v>
       </c>
       <c r="E112" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F112">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
@@ -3777,10 +3789,10 @@
         <v>95</v>
       </c>
       <c r="E113" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F113">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3797,10 +3809,10 @@
         <v>95</v>
       </c>
       <c r="E114" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F114">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -3817,10 +3829,10 @@
         <v>95</v>
       </c>
       <c r="E115" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F115">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -3837,15 +3849,15 @@
         <v>95</v>
       </c>
       <c r="E116" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F116">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B117" t="s">
         <v>7</v>
@@ -3854,18 +3866,18 @@
         <v>46</v>
       </c>
       <c r="D117" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E117" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B118" t="s">
         <v>7</v>
@@ -3874,13 +3886,13 @@
         <v>46</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="E118" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="F118">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -3897,10 +3909,10 @@
         <v>108</v>
       </c>
       <c r="E119" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="F119">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -3917,15 +3929,15 @@
         <v>108</v>
       </c>
       <c r="E120" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F120">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B121" t="s">
         <v>7</v>
@@ -3934,18 +3946,18 @@
         <v>46</v>
       </c>
       <c r="D121" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E121" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="B122" t="s">
         <v>7</v>
@@ -3954,13 +3966,13 @@
         <v>46</v>
       </c>
       <c r="D122" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="E122" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F122">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -3977,15 +3989,15 @@
         <v>114</v>
       </c>
       <c r="E123" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F123">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B124" t="s">
         <v>7</v>
@@ -3994,18 +4006,18 @@
         <v>46</v>
       </c>
       <c r="D124" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E124" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B125" t="s">
         <v>7</v>
@@ -4014,18 +4026,18 @@
         <v>46</v>
       </c>
       <c r="D125" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E125" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="F125">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B126" t="s">
         <v>7</v>
@@ -4034,10 +4046,10 @@
         <v>46</v>
       </c>
       <c r="D126" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E126" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F126">
         <v>1</v>
@@ -4045,7 +4057,7 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B127" t="s">
         <v>7</v>
@@ -4054,10 +4066,10 @@
         <v>46</v>
       </c>
       <c r="D127" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E127" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="F127">
         <v>2</v>
@@ -4077,10 +4089,10 @@
         <v>123</v>
       </c>
       <c r="E128" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F128">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4097,10 +4109,10 @@
         <v>123</v>
       </c>
       <c r="E129" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F129">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4117,10 +4129,10 @@
         <v>123</v>
       </c>
       <c r="E130" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F130">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -4137,10 +4149,10 @@
         <v>123</v>
       </c>
       <c r="E131" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F131">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -4157,10 +4169,10 @@
         <v>123</v>
       </c>
       <c r="E132" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F132">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -4177,10 +4189,10 @@
         <v>123</v>
       </c>
       <c r="E133" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F133">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -4197,15 +4209,15 @@
         <v>123</v>
       </c>
       <c r="E134" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F134">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B135" t="s">
         <v>7</v>
@@ -4214,18 +4226,18 @@
         <v>46</v>
       </c>
       <c r="D135" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E135" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F135">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B136" t="s">
         <v>7</v>
@@ -4234,13 +4246,13 @@
         <v>46</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E136" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F136">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
@@ -4257,15 +4269,15 @@
         <v>134</v>
       </c>
       <c r="E137" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F137">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B138" t="s">
         <v>7</v>
@@ -4274,18 +4286,18 @@
         <v>46</v>
       </c>
       <c r="D138" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E138" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F138">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="B139" t="s">
         <v>7</v>
@@ -4294,13 +4306,13 @@
         <v>46</v>
       </c>
       <c r="D139" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E139" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F139">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -4317,10 +4329,10 @@
         <v>139</v>
       </c>
       <c r="E140" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F140">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -4337,15 +4349,15 @@
         <v>139</v>
       </c>
       <c r="E141" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F141">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B142" t="s">
         <v>7</v>
@@ -4354,18 +4366,18 @@
         <v>46</v>
       </c>
       <c r="D142" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E142" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="F142">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
         <v>7</v>
@@ -4374,18 +4386,18 @@
         <v>46</v>
       </c>
       <c r="D143" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E143" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="F143">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B144" t="s">
         <v>7</v>
@@ -4394,10 +4406,10 @@
         <v>46</v>
       </c>
       <c r="D144" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E144" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F144">
         <v>1</v>
@@ -4405,7 +4417,7 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="B145" t="s">
         <v>7</v>
@@ -4414,10 +4426,10 @@
         <v>46</v>
       </c>
       <c r="D145" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E145" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F145">
         <v>2</v>
@@ -4437,10 +4449,10 @@
         <v>149</v>
       </c>
       <c r="E146" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F146">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -4457,10 +4469,10 @@
         <v>149</v>
       </c>
       <c r="E147" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F147">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -4477,10 +4489,10 @@
         <v>149</v>
       </c>
       <c r="E148" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="F148">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -4497,15 +4509,15 @@
         <v>149</v>
       </c>
       <c r="E149" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="F149">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B150" t="s">
         <v>7</v>
@@ -4514,18 +4526,18 @@
         <v>46</v>
       </c>
       <c r="D150" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E150" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F150">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="B151" t="s">
         <v>7</v>
@@ -4534,13 +4546,13 @@
         <v>46</v>
       </c>
       <c r="D151" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E151" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F151">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4557,10 +4569,10 @@
         <v>156</v>
       </c>
       <c r="E152" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F152">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4577,10 +4589,10 @@
         <v>156</v>
       </c>
       <c r="E153" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F153">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4597,10 +4609,10 @@
         <v>156</v>
       </c>
       <c r="E154" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F154">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -4617,10 +4629,10 @@
         <v>156</v>
       </c>
       <c r="E155" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F155">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -4637,10 +4649,10 @@
         <v>156</v>
       </c>
       <c r="E156" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F156">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -4657,10 +4669,10 @@
         <v>156</v>
       </c>
       <c r="E157" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F157">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -4677,10 +4689,10 @@
         <v>156</v>
       </c>
       <c r="E158" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F158">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -4697,253 +4709,265 @@
         <v>156</v>
       </c>
       <c r="E159" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F159">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
+        <v>155</v>
+      </c>
+      <c r="B160" t="s">
+        <v>7</v>
+      </c>
+      <c r="C160" t="s">
+        <v>46</v>
+      </c>
+      <c r="D160" t="s">
+        <v>156</v>
+      </c>
+      <c r="E160" t="s">
+        <v>165</v>
+      </c>
+      <c r="F160">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>155</v>
+      </c>
+      <c r="B161" t="s">
+        <v>7</v>
+      </c>
+      <c r="C161" t="s">
+        <v>46</v>
+      </c>
+      <c r="D161" t="s">
+        <v>156</v>
+      </c>
+      <c r="E161" t="s">
+        <v>166</v>
+      </c>
+      <c r="F161">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
         <v>167</v>
       </c>
-      <c r="B160" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" t="s">
-        <v>168</v>
-      </c>
-      <c r="D160" t="s">
+      <c r="B162" t="s">
+        <v>7</v>
+      </c>
+      <c r="C162" t="s">
+        <v>168</v>
+      </c>
+      <c r="D162" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A161" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
         <v>170</v>
       </c>
-      <c r="B161" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" t="s">
-        <v>168</v>
-      </c>
-      <c r="D161" t="s">
+      <c r="B163" t="s">
+        <v>7</v>
+      </c>
+      <c r="C163" t="s">
+        <v>168</v>
+      </c>
+      <c r="D163" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
         <v>172</v>
       </c>
-      <c r="B162" t="s">
-        <v>7</v>
-      </c>
-      <c r="C162" t="s">
-        <v>168</v>
-      </c>
-      <c r="D162" t="s">
+      <c r="B164" t="s">
+        <v>7</v>
+      </c>
+      <c r="C164" t="s">
+        <v>168</v>
+      </c>
+      <c r="D164" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
         <v>174</v>
       </c>
-      <c r="B163" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" t="s">
-        <v>168</v>
-      </c>
-      <c r="D163" t="s">
+      <c r="B165" t="s">
+        <v>7</v>
+      </c>
+      <c r="C165" t="s">
+        <v>168</v>
+      </c>
+      <c r="D165" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
         <v>176</v>
       </c>
-      <c r="B164" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" t="s">
-        <v>168</v>
-      </c>
-      <c r="D164" t="s">
+      <c r="B166" t="s">
+        <v>7</v>
+      </c>
+      <c r="C166" t="s">
+        <v>168</v>
+      </c>
+      <c r="D166" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
         <v>178</v>
       </c>
-      <c r="B165" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" t="s">
-        <v>168</v>
-      </c>
-      <c r="D165" t="s">
+      <c r="B167" t="s">
+        <v>7</v>
+      </c>
+      <c r="C167" t="s">
+        <v>168</v>
+      </c>
+      <c r="D167" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A166" t="s">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
         <v>180</v>
       </c>
-      <c r="B166" t="s">
-        <v>7</v>
-      </c>
-      <c r="C166" t="s">
-        <v>168</v>
-      </c>
-      <c r="D166" t="s">
+      <c r="B168" t="s">
+        <v>7</v>
+      </c>
+      <c r="C168" t="s">
+        <v>168</v>
+      </c>
+      <c r="D168" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A167" t="s">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
         <v>182</v>
       </c>
-      <c r="B167" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" t="s">
-        <v>168</v>
-      </c>
-      <c r="D167" t="s">
+      <c r="B169" t="s">
+        <v>7</v>
+      </c>
+      <c r="C169" t="s">
+        <v>168</v>
+      </c>
+      <c r="D169" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A168" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
         <v>184</v>
       </c>
-      <c r="B168" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" t="s">
-        <v>168</v>
-      </c>
-      <c r="D168" t="s">
+      <c r="B170" t="s">
+        <v>7</v>
+      </c>
+      <c r="C170" t="s">
+        <v>168</v>
+      </c>
+      <c r="D170" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A169" t="s">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
         <v>186</v>
       </c>
-      <c r="B169" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" t="s">
-        <v>168</v>
-      </c>
-      <c r="D169" t="s">
+      <c r="B171" t="s">
+        <v>7</v>
+      </c>
+      <c r="C171" t="s">
+        <v>168</v>
+      </c>
+      <c r="D171" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
         <v>188</v>
       </c>
-      <c r="B170" t="s">
-        <v>7</v>
-      </c>
-      <c r="C170" t="s">
-        <v>168</v>
-      </c>
-      <c r="D170" t="s">
+      <c r="B172" t="s">
+        <v>7</v>
+      </c>
+      <c r="C172" t="s">
+        <v>168</v>
+      </c>
+      <c r="D172" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A171" t="s">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
         <v>190</v>
       </c>
-      <c r="B171" t="s">
-        <v>7</v>
-      </c>
-      <c r="C171" t="s">
-        <v>168</v>
-      </c>
-      <c r="D171" t="s">
+      <c r="B173" t="s">
+        <v>7</v>
+      </c>
+      <c r="C173" t="s">
+        <v>168</v>
+      </c>
+      <c r="D173" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A172" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
         <v>192</v>
       </c>
-      <c r="B172" t="s">
-        <v>7</v>
-      </c>
-      <c r="C172" t="s">
-        <v>168</v>
-      </c>
-      <c r="D172" t="s">
+      <c r="B174" t="s">
+        <v>7</v>
+      </c>
+      <c r="C174" t="s">
+        <v>168</v>
+      </c>
+      <c r="D174" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A173" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
         <v>194</v>
       </c>
-      <c r="B173" t="s">
-        <v>7</v>
-      </c>
-      <c r="C173" t="s">
-        <v>168</v>
-      </c>
-      <c r="D173" t="s">
+      <c r="B175" t="s">
+        <v>7</v>
+      </c>
+      <c r="C175" t="s">
+        <v>168</v>
+      </c>
+      <c r="D175" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A174" t="s">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
         <v>196</v>
       </c>
-      <c r="B174" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" t="s">
-        <v>168</v>
-      </c>
-      <c r="D174" t="s">
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>168</v>
+      </c>
+      <c r="D176" t="s">
         <v>197</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A175" t="s">
-        <v>198</v>
-      </c>
-      <c r="B175" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" t="s">
-        <v>168</v>
-      </c>
-      <c r="D175" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A176" t="s">
-        <v>200</v>
-      </c>
-      <c r="B176" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" t="s">
-        <v>168</v>
-      </c>
-      <c r="D176" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="B177" t="s">
         <v>7</v>
@@ -4952,12 +4976,12 @@
         <v>168</v>
       </c>
       <c r="D177" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B178" t="s">
         <v>7</v>
@@ -4966,12 +4990,12 @@
         <v>168</v>
       </c>
       <c r="D178" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B179" t="s">
         <v>7</v>
@@ -4980,12 +5004,12 @@
         <v>168</v>
       </c>
       <c r="D179" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B180" t="s">
         <v>7</v>
@@ -4994,12 +5018,12 @@
         <v>168</v>
       </c>
       <c r="D180" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B181" t="s">
         <v>7</v>
@@ -5008,12 +5032,12 @@
         <v>168</v>
       </c>
       <c r="D181" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B182" t="s">
         <v>7</v>
@@ -5022,12 +5046,12 @@
         <v>168</v>
       </c>
       <c r="D182" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B183" t="s">
         <v>7</v>
@@ -5036,12 +5060,12 @@
         <v>168</v>
       </c>
       <c r="D183" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B184" t="s">
         <v>7</v>
@@ -5050,12 +5074,12 @@
         <v>168</v>
       </c>
       <c r="D184" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B185" t="s">
         <v>7</v>
@@ -5064,12 +5088,12 @@
         <v>168</v>
       </c>
       <c r="D185" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B186" t="s">
         <v>7</v>
@@ -5078,12 +5102,12 @@
         <v>168</v>
       </c>
       <c r="D186" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B187" t="s">
         <v>7</v>
@@ -5092,12 +5116,12 @@
         <v>168</v>
       </c>
       <c r="D187" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="B188" t="s">
         <v>7</v>
@@ -5106,12 +5130,12 @@
         <v>168</v>
       </c>
       <c r="D188" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B189" t="s">
         <v>7</v>
@@ -5120,52 +5144,40 @@
         <v>168</v>
       </c>
       <c r="D189" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="B190" t="s">
         <v>7</v>
       </c>
       <c r="C190" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D190" t="s">
-        <v>230</v>
-      </c>
-      <c r="E190" t="s">
-        <v>231</v>
-      </c>
-      <c r="F190">
-        <v>1</v>
+        <v>225</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B191" t="s">
         <v>7</v>
       </c>
       <c r="C191" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D191" t="s">
-        <v>230</v>
-      </c>
-      <c r="E191" t="s">
-        <v>232</v>
-      </c>
-      <c r="F191">
-        <v>2</v>
+        <v>227</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B192" t="s">
         <v>7</v>
@@ -5174,10 +5186,10 @@
         <v>229</v>
       </c>
       <c r="D192" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E192" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F192">
         <v>1</v>
@@ -5185,7 +5197,7 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B193" t="s">
         <v>7</v>
@@ -5194,10 +5206,10 @@
         <v>229</v>
       </c>
       <c r="D193" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E193" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="F193">
         <v>2</v>
@@ -5205,7 +5217,7 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B194" t="s">
         <v>7</v>
@@ -5214,12 +5226,18 @@
         <v>229</v>
       </c>
       <c r="D194" t="s">
-        <v>238</v>
+        <v>234</v>
+      </c>
+      <c r="E194" t="s">
+        <v>235</v>
+      </c>
+      <c r="F194">
+        <v>1</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B195" t="s">
         <v>7</v>
@@ -5228,12 +5246,18 @@
         <v>229</v>
       </c>
       <c r="D195" t="s">
-        <v>240</v>
+        <v>234</v>
+      </c>
+      <c r="E195" t="s">
+        <v>236</v>
+      </c>
+      <c r="F195">
+        <v>2</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B196" t="s">
         <v>7</v>
@@ -5242,12 +5266,12 @@
         <v>229</v>
       </c>
       <c r="D196" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B197" t="s">
         <v>7</v>
@@ -5256,12 +5280,12 @@
         <v>229</v>
       </c>
       <c r="D197" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B198" t="s">
         <v>7</v>
@@ -5270,12 +5294,12 @@
         <v>229</v>
       </c>
       <c r="D198" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B199" t="s">
         <v>7</v>
@@ -5284,47 +5308,35 @@
         <v>229</v>
       </c>
       <c r="D199" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B200" t="s">
         <v>7</v>
       </c>
       <c r="C200" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="D200" t="s">
-        <v>251</v>
-      </c>
-      <c r="E200" t="s">
-        <v>252</v>
-      </c>
-      <c r="F200">
-        <v>-1</v>
+        <v>246</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B201" t="s">
         <v>7</v>
       </c>
       <c r="C201" t="s">
-        <v>250</v>
+        <v>229</v>
       </c>
       <c r="D201" t="s">
-        <v>251</v>
-      </c>
-      <c r="E201" t="s">
-        <v>253</v>
-      </c>
-      <c r="F201">
-        <v>0</v>
+        <v>248</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -5341,15 +5353,15 @@
         <v>251</v>
       </c>
       <c r="E202" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F202">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B203" t="s">
         <v>7</v>
@@ -5361,15 +5373,15 @@
         <v>251</v>
       </c>
       <c r="E203" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F203">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B204" t="s">
         <v>7</v>
@@ -5381,10 +5393,10 @@
         <v>251</v>
       </c>
       <c r="E204" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F204">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -5401,15 +5413,15 @@
         <v>251</v>
       </c>
       <c r="E205" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F205">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B206" t="s">
         <v>7</v>
@@ -5421,15 +5433,15 @@
         <v>251</v>
       </c>
       <c r="E206" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F206">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B207" t="s">
         <v>7</v>
@@ -5441,10 +5453,10 @@
         <v>251</v>
       </c>
       <c r="E207" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F207">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -5461,15 +5473,15 @@
         <v>251</v>
       </c>
       <c r="E208" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F208">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B209" t="s">
         <v>7</v>
@@ -5481,15 +5493,15 @@
         <v>251</v>
       </c>
       <c r="E209" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F209">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B210" t="s">
         <v>7</v>
@@ -5501,10 +5513,10 @@
         <v>251</v>
       </c>
       <c r="E210" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F210">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -5521,15 +5533,15 @@
         <v>251</v>
       </c>
       <c r="E211" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F211">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B212" t="s">
         <v>7</v>
@@ -5541,15 +5553,15 @@
         <v>251</v>
       </c>
       <c r="E212" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F212">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B213" t="s">
         <v>7</v>
@@ -5561,10 +5573,10 @@
         <v>251</v>
       </c>
       <c r="E213" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F213">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -5581,15 +5593,15 @@
         <v>251</v>
       </c>
       <c r="E214" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F214">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B215" t="s">
         <v>7</v>
@@ -5601,15 +5613,15 @@
         <v>251</v>
       </c>
       <c r="E215" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F215">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B216" t="s">
         <v>7</v>
@@ -5621,10 +5633,10 @@
         <v>251</v>
       </c>
       <c r="E216" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F216">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,15 +5653,15 @@
         <v>251</v>
       </c>
       <c r="E217" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F217">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B218" t="s">
         <v>7</v>
@@ -5661,15 +5673,15 @@
         <v>251</v>
       </c>
       <c r="E218" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F218">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B219" t="s">
         <v>7</v>
@@ -5681,10 +5693,10 @@
         <v>251</v>
       </c>
       <c r="E219" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F219">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -5701,15 +5713,15 @@
         <v>251</v>
       </c>
       <c r="E220" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F220">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B221" t="s">
         <v>7</v>
@@ -5721,15 +5733,15 @@
         <v>251</v>
       </c>
       <c r="E221" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F221">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B222" t="s">
         <v>7</v>
@@ -5741,10 +5753,10 @@
         <v>251</v>
       </c>
       <c r="E222" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F222">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -5761,15 +5773,15 @@
         <v>251</v>
       </c>
       <c r="E223" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B224" t="s">
         <v>7</v>
@@ -5781,15 +5793,15 @@
         <v>251</v>
       </c>
       <c r="E224" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F224">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B225" t="s">
         <v>7</v>
@@ -5801,10 +5813,10 @@
         <v>251</v>
       </c>
       <c r="E225" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F225">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -5821,15 +5833,15 @@
         <v>251</v>
       </c>
       <c r="E226" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F226">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B227" t="s">
         <v>7</v>
@@ -5841,15 +5853,15 @@
         <v>251</v>
       </c>
       <c r="E227" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F227">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B228" t="s">
         <v>7</v>
@@ -5861,10 +5873,10 @@
         <v>251</v>
       </c>
       <c r="E228" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F228">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -5881,15 +5893,15 @@
         <v>251</v>
       </c>
       <c r="E229" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F229">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B230" t="s">
         <v>7</v>
@@ -5901,15 +5913,15 @@
         <v>251</v>
       </c>
       <c r="E230" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F230">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B231" t="s">
         <v>7</v>
@@ -5921,10 +5933,10 @@
         <v>251</v>
       </c>
       <c r="E231" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
@@ -5941,43 +5953,55 @@
         <v>251</v>
       </c>
       <c r="E232" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F232">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B233" t="s">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="C233" t="s">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="D233" t="s">
-        <v>9</v>
+        <v>251</v>
+      </c>
+      <c r="E233" t="s">
+        <v>253</v>
+      </c>
+      <c r="F233">
+        <v>0</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B234" t="s">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="C234" t="s">
-        <v>8</v>
+        <v>250</v>
       </c>
       <c r="D234" t="s">
-        <v>11</v>
+        <v>251</v>
+      </c>
+      <c r="E234" t="s">
+        <v>254</v>
+      </c>
+      <c r="F234">
+        <v>1</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B235" t="s">
         <v>266</v>
@@ -5986,12 +6010,12 @@
         <v>8</v>
       </c>
       <c r="D235" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B236" t="s">
         <v>266</v>
@@ -6000,12 +6024,12 @@
         <v>8</v>
       </c>
       <c r="D236" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B237" t="s">
         <v>266</v>
@@ -6014,40 +6038,40 @@
         <v>8</v>
       </c>
       <c r="D237" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>167</v>
+        <v>269</v>
       </c>
       <c r="B238" t="s">
         <v>266</v>
       </c>
       <c r="C238" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="D238" t="s">
-        <v>271</v>
+        <v>15</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>172</v>
+        <v>270</v>
       </c>
       <c r="B239" t="s">
         <v>266</v>
       </c>
       <c r="C239" t="s">
-        <v>168</v>
+        <v>8</v>
       </c>
       <c r="D239" t="s">
-        <v>272</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="B240" t="s">
         <v>266</v>
@@ -6056,12 +6080,12 @@
         <v>168</v>
       </c>
       <c r="D240" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B241" t="s">
         <v>266</v>
@@ -6070,12 +6094,12 @@
         <v>168</v>
       </c>
       <c r="D241" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B242" t="s">
         <v>266</v>
@@ -6084,12 +6108,12 @@
         <v>168</v>
       </c>
       <c r="D242" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B243" t="s">
         <v>266</v>
@@ -6098,12 +6122,12 @@
         <v>168</v>
       </c>
       <c r="D243" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B244" t="s">
         <v>266</v>
@@ -6112,12 +6136,12 @@
         <v>168</v>
       </c>
       <c r="D244" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B245" t="s">
         <v>266</v>
@@ -6126,12 +6150,12 @@
         <v>168</v>
       </c>
       <c r="D245" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B246" t="s">
         <v>266</v>
@@ -6140,12 +6164,12 @@
         <v>168</v>
       </c>
       <c r="D246" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B247" t="s">
         <v>266</v>
@@ -6154,12 +6178,12 @@
         <v>168</v>
       </c>
       <c r="D247" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B248" t="s">
         <v>266</v>
@@ -6168,12 +6192,12 @@
         <v>168</v>
       </c>
       <c r="D248" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B249" t="s">
         <v>266</v>
@@ -6182,12 +6206,12 @@
         <v>168</v>
       </c>
       <c r="D249" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B250" t="s">
         <v>266</v>
@@ -6196,12 +6220,12 @@
         <v>168</v>
       </c>
       <c r="D250" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>284</v>
+        <v>192</v>
       </c>
       <c r="B251" t="s">
         <v>266</v>
@@ -6210,12 +6234,12 @@
         <v>168</v>
       </c>
       <c r="D251" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>286</v>
+        <v>170</v>
       </c>
       <c r="B252" t="s">
         <v>266</v>
@@ -6224,12 +6248,12 @@
         <v>168</v>
       </c>
       <c r="D252" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B253" t="s">
         <v>266</v>
@@ -6238,12 +6262,12 @@
         <v>168</v>
       </c>
       <c r="D253" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B254" t="s">
         <v>266</v>
@@ -6252,12 +6276,12 @@
         <v>168</v>
       </c>
       <c r="D254" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B255" t="s">
         <v>266</v>
@@ -6266,12 +6290,12 @@
         <v>168</v>
       </c>
       <c r="D255" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B256" t="s">
         <v>266</v>
@@ -6280,12 +6304,12 @@
         <v>168</v>
       </c>
       <c r="D256" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B257" t="s">
         <v>266</v>
@@ -6294,12 +6318,12 @@
         <v>168</v>
       </c>
       <c r="D257" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B258" t="s">
         <v>266</v>
@@ -6308,12 +6332,12 @@
         <v>168</v>
       </c>
       <c r="D258" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B259" t="s">
         <v>266</v>
@@ -6322,12 +6346,12 @@
         <v>168</v>
       </c>
       <c r="D259" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B260" t="s">
         <v>266</v>
@@ -6336,12 +6360,12 @@
         <v>168</v>
       </c>
       <c r="D260" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B261" t="s">
         <v>266</v>
@@ -6350,12 +6374,12 @@
         <v>168</v>
       </c>
       <c r="D261" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B262" t="s">
         <v>266</v>
@@ -6364,12 +6388,12 @@
         <v>168</v>
       </c>
       <c r="D262" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B263" t="s">
         <v>266</v>
@@ -6378,12 +6402,12 @@
         <v>168</v>
       </c>
       <c r="D263" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B264" t="s">
         <v>266</v>
@@ -6392,12 +6416,12 @@
         <v>168</v>
       </c>
       <c r="D264" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B265" t="s">
         <v>266</v>
@@ -6406,12 +6430,12 @@
         <v>168</v>
       </c>
       <c r="D265" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B266" t="s">
         <v>266</v>
@@ -6420,12 +6444,12 @@
         <v>168</v>
       </c>
       <c r="D266" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B267" t="s">
         <v>266</v>
@@ -6434,12 +6458,12 @@
         <v>168</v>
       </c>
       <c r="D267" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B268" t="s">
         <v>266</v>
@@ -6448,12 +6472,12 @@
         <v>168</v>
       </c>
       <c r="D268" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B269" t="s">
         <v>266</v>
@@ -6462,12 +6486,12 @@
         <v>168</v>
       </c>
       <c r="D269" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B270" t="s">
         <v>266</v>
@@ -6476,12 +6500,12 @@
         <v>168</v>
       </c>
       <c r="D270" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B271" t="s">
         <v>266</v>
@@ -6490,12 +6514,12 @@
         <v>168</v>
       </c>
       <c r="D271" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B272" t="s">
         <v>266</v>
@@ -6504,12 +6528,12 @@
         <v>168</v>
       </c>
       <c r="D272" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B273" t="s">
         <v>266</v>
@@ -6518,12 +6542,12 @@
         <v>168</v>
       </c>
       <c r="D273" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B274" t="s">
         <v>266</v>
@@ -6532,12 +6556,12 @@
         <v>168</v>
       </c>
       <c r="D274" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B275" t="s">
         <v>266</v>
@@ -6546,12 +6570,12 @@
         <v>168</v>
       </c>
       <c r="D275" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B276" t="s">
         <v>266</v>
@@ -6560,12 +6584,12 @@
         <v>168</v>
       </c>
       <c r="D276" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B277" t="s">
         <v>266</v>
@@ -6574,12 +6598,12 @@
         <v>168</v>
       </c>
       <c r="D277" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B278" t="s">
         <v>266</v>
@@ -6588,12 +6612,12 @@
         <v>168</v>
       </c>
       <c r="D278" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B279" t="s">
         <v>266</v>
@@ -6602,12 +6626,12 @@
         <v>168</v>
       </c>
       <c r="D279" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="B280" t="s">
         <v>266</v>
@@ -6616,12 +6640,12 @@
         <v>168</v>
       </c>
       <c r="D280" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>202</v>
+        <v>340</v>
       </c>
       <c r="B281" t="s">
         <v>266</v>
@@ -6630,12 +6654,12 @@
         <v>168</v>
       </c>
       <c r="D281" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B282" t="s">
         <v>266</v>
@@ -6644,12 +6668,12 @@
         <v>168</v>
       </c>
       <c r="D282" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B283" t="s">
         <v>266</v>
@@ -6658,12 +6682,12 @@
         <v>168</v>
       </c>
       <c r="D283" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B284" t="s">
         <v>266</v>
@@ -6672,12 +6696,12 @@
         <v>168</v>
       </c>
       <c r="D284" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B285" t="s">
         <v>266</v>
@@ -6686,12 +6710,12 @@
         <v>168</v>
       </c>
       <c r="D285" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B286" t="s">
         <v>266</v>
@@ -6700,12 +6724,12 @@
         <v>168</v>
       </c>
       <c r="D286" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B287" t="s">
         <v>266</v>
@@ -6714,12 +6738,12 @@
         <v>168</v>
       </c>
       <c r="D287" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B288" t="s">
         <v>266</v>
@@ -6728,12 +6752,12 @@
         <v>168</v>
       </c>
       <c r="D288" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B289" t="s">
         <v>266</v>
@@ -6742,12 +6766,12 @@
         <v>168</v>
       </c>
       <c r="D289" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B290" t="s">
         <v>266</v>
@@ -6756,12 +6780,12 @@
         <v>168</v>
       </c>
       <c r="D290" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B291" t="s">
         <v>266</v>
@@ -6770,12 +6794,12 @@
         <v>168</v>
       </c>
       <c r="D291" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B292" t="s">
         <v>266</v>
@@ -6784,12 +6808,12 @@
         <v>168</v>
       </c>
       <c r="D292" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>355</v>
+        <v>222</v>
       </c>
       <c r="B293" t="s">
         <v>266</v>
@@ -6798,12 +6822,12 @@
         <v>168</v>
       </c>
       <c r="D293" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>357</v>
+        <v>200</v>
       </c>
       <c r="B294" t="s">
         <v>266</v>
@@ -6812,12 +6836,12 @@
         <v>168</v>
       </c>
       <c r="D294" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B295" t="s">
         <v>266</v>
@@ -6826,12 +6850,12 @@
         <v>168</v>
       </c>
       <c r="D295" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B296" t="s">
         <v>266</v>
@@ -6840,12 +6864,12 @@
         <v>168</v>
       </c>
       <c r="D296" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B297" t="s">
         <v>266</v>
@@ -6854,12 +6878,12 @@
         <v>168</v>
       </c>
       <c r="D297" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B298" t="s">
         <v>266</v>
@@ -6868,12 +6892,12 @@
         <v>168</v>
       </c>
       <c r="D298" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B299" t="s">
         <v>266</v>
@@ -6882,12 +6906,12 @@
         <v>168</v>
       </c>
       <c r="D299" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B300" t="s">
         <v>266</v>
@@ -6896,12 +6920,12 @@
         <v>168</v>
       </c>
       <c r="D300" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B301" t="s">
         <v>266</v>
@@ -6910,12 +6934,12 @@
         <v>168</v>
       </c>
       <c r="D301" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B302" t="s">
         <v>266</v>
@@ -6924,12 +6948,12 @@
         <v>168</v>
       </c>
       <c r="D302" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B303" t="s">
         <v>266</v>
@@ -6938,12 +6962,12 @@
         <v>168</v>
       </c>
       <c r="D303" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B304" t="s">
         <v>266</v>
@@ -6952,12 +6976,12 @@
         <v>168</v>
       </c>
       <c r="D304" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B305" t="s">
         <v>266</v>
@@ -6966,12 +6990,12 @@
         <v>168</v>
       </c>
       <c r="D305" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B306" t="s">
         <v>266</v>
@@ -6980,12 +7004,12 @@
         <v>168</v>
       </c>
       <c r="D306" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B307" t="s">
         <v>266</v>
@@ -6994,12 +7018,12 @@
         <v>168</v>
       </c>
       <c r="D307" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B308" t="s">
         <v>266</v>
@@ -7008,12 +7032,12 @@
         <v>168</v>
       </c>
       <c r="D308" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B309" t="s">
         <v>266</v>
@@ -7022,12 +7046,12 @@
         <v>168</v>
       </c>
       <c r="D309" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B310" t="s">
         <v>266</v>
@@ -7036,12 +7060,12 @@
         <v>168</v>
       </c>
       <c r="D310" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B311" t="s">
         <v>266</v>
@@ -7050,12 +7074,12 @@
         <v>168</v>
       </c>
       <c r="D311" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B312" t="s">
         <v>266</v>
@@ -7064,12 +7088,12 @@
         <v>168</v>
       </c>
       <c r="D312" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B313" t="s">
         <v>266</v>
@@ -7078,12 +7102,12 @@
         <v>168</v>
       </c>
       <c r="D313" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B314" t="s">
         <v>266</v>
@@ -7092,12 +7116,12 @@
         <v>168</v>
       </c>
       <c r="D314" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B315" t="s">
         <v>266</v>
@@ -7106,12 +7130,12 @@
         <v>168</v>
       </c>
       <c r="D315" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B316" t="s">
         <v>266</v>
@@ -7120,12 +7144,12 @@
         <v>168</v>
       </c>
       <c r="D316" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B317" t="s">
         <v>266</v>
@@ -7134,12 +7158,12 @@
         <v>168</v>
       </c>
       <c r="D317" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B318" t="s">
         <v>266</v>
@@ -7148,12 +7172,12 @@
         <v>168</v>
       </c>
       <c r="D318" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B319" t="s">
         <v>266</v>
@@ -7162,12 +7186,12 @@
         <v>168</v>
       </c>
       <c r="D319" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B320" t="s">
         <v>266</v>
@@ -7176,12 +7200,12 @@
         <v>168</v>
       </c>
       <c r="D320" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B321" t="s">
         <v>266</v>
@@ -7190,68 +7214,68 @@
         <v>168</v>
       </c>
       <c r="D321" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>245</v>
+        <v>409</v>
       </c>
       <c r="B322" t="s">
         <v>266</v>
       </c>
       <c r="C322" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D322" t="s">
-        <v>246</v>
+        <v>410</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>247</v>
+        <v>411</v>
       </c>
       <c r="B323" t="s">
         <v>266</v>
       </c>
       <c r="C323" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D323" t="s">
-        <v>248</v>
+        <v>412</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>413</v>
+        <v>245</v>
       </c>
       <c r="B324" t="s">
         <v>266</v>
       </c>
       <c r="C324" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="D324" t="s">
-        <v>414</v>
+        <v>246</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>415</v>
+        <v>247</v>
       </c>
       <c r="B325" t="s">
         <v>266</v>
       </c>
       <c r="C325" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="D325" t="s">
-        <v>416</v>
+        <v>248</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B326" t="s">
         <v>266</v>
@@ -7260,12 +7284,12 @@
         <v>7</v>
       </c>
       <c r="D326" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B327" t="s">
         <v>266</v>
@@ -7274,12 +7298,12 @@
         <v>7</v>
       </c>
       <c r="D327" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B328" t="s">
         <v>266</v>
@@ -7288,12 +7312,12 @@
         <v>7</v>
       </c>
       <c r="D328" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B329" t="s">
         <v>266</v>
@@ -7302,12 +7326,12 @@
         <v>7</v>
       </c>
       <c r="D329" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B330" t="s">
         <v>266</v>
@@ -7316,12 +7340,12 @@
         <v>7</v>
       </c>
       <c r="D330" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B331" t="s">
         <v>266</v>
@@ -7330,12 +7354,12 @@
         <v>7</v>
       </c>
       <c r="D331" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B332" t="s">
         <v>266</v>
@@ -7344,12 +7368,12 @@
         <v>7</v>
       </c>
       <c r="D332" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B333" t="s">
         <v>266</v>
@@ -7358,12 +7382,12 @@
         <v>7</v>
       </c>
       <c r="D333" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B334" t="s">
         <v>266</v>
@@ -7372,12 +7396,12 @@
         <v>7</v>
       </c>
       <c r="D334" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B335" t="s">
         <v>266</v>
@@ -7386,25 +7410,53 @@
         <v>7</v>
       </c>
       <c r="D335" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
+        <v>433</v>
+      </c>
+      <c r="B336" t="s">
+        <v>266</v>
+      </c>
+      <c r="C336" t="s">
+        <v>7</v>
+      </c>
+      <c r="D336" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A337" t="s">
+        <v>435</v>
+      </c>
+      <c r="B337" t="s">
+        <v>266</v>
+      </c>
+      <c r="C337" t="s">
+        <v>7</v>
+      </c>
+      <c r="D337" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A338" t="s">
         <v>437</v>
       </c>
-      <c r="B336" t="s">
-        <v>266</v>
-      </c>
-      <c r="C336" t="s">
-        <v>7</v>
-      </c>
-      <c r="D336" t="s">
+      <c r="B338" t="s">
+        <v>266</v>
+      </c>
+      <c r="C338" t="s">
+        <v>7</v>
+      </c>
+      <c r="D338" t="s">
         <v>438</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F336" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F338" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data-raw/xlsx/tabla_etiquetas.xlsx
+++ b/data-raw/xlsx/tabla_etiquetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fernando_gallegos\Proyectos\odsa.eusilc\data-raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10A217F-123A-45AF-BD81-CEB3BA3AB1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F31B970-14D0-47E3-96E9-34C2E00A507C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$338</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$340</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1549" uniqueCount="445">
   <si>
     <t>variable</t>
   </si>
@@ -1360,6 +1360,9 @@
   </si>
   <si>
     <t>Rural</t>
+  </si>
+  <si>
+    <t>hi07</t>
   </si>
 </sst>
 </file>
@@ -1599,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F338"/>
+  <dimension ref="A1:F340"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -6071,245 +6074,257 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>444</v>
+      </c>
+      <c r="B240" t="s">
+        <v>266</v>
+      </c>
+      <c r="C240" t="s">
+        <v>8</v>
+      </c>
+      <c r="D240" t="s">
+        <v>441</v>
+      </c>
+      <c r="E240" t="s">
+        <v>442</v>
+      </c>
+      <c r="F240">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>444</v>
+      </c>
+      <c r="B241" t="s">
+        <v>266</v>
+      </c>
+      <c r="C241" t="s">
+        <v>8</v>
+      </c>
+      <c r="D241" t="s">
+        <v>441</v>
+      </c>
+      <c r="E241" t="s">
+        <v>443</v>
+      </c>
+      <c r="F241">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
         <v>167</v>
       </c>
-      <c r="B240" t="s">
-        <v>266</v>
-      </c>
-      <c r="C240" t="s">
-        <v>168</v>
-      </c>
-      <c r="D240" t="s">
+      <c r="B242" t="s">
+        <v>266</v>
+      </c>
+      <c r="C242" t="s">
+        <v>168</v>
+      </c>
+      <c r="D242" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A241" t="s">
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
         <v>172</v>
       </c>
-      <c r="B241" t="s">
-        <v>266</v>
-      </c>
-      <c r="C241" t="s">
-        <v>168</v>
-      </c>
-      <c r="D241" t="s">
+      <c r="B243" t="s">
+        <v>266</v>
+      </c>
+      <c r="C243" t="s">
+        <v>168</v>
+      </c>
+      <c r="D243" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A242" t="s">
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
         <v>174</v>
       </c>
-      <c r="B242" t="s">
-        <v>266</v>
-      </c>
-      <c r="C242" t="s">
-        <v>168</v>
-      </c>
-      <c r="D242" t="s">
+      <c r="B244" t="s">
+        <v>266</v>
+      </c>
+      <c r="C244" t="s">
+        <v>168</v>
+      </c>
+      <c r="D244" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
         <v>176</v>
       </c>
-      <c r="B243" t="s">
-        <v>266</v>
-      </c>
-      <c r="C243" t="s">
-        <v>168</v>
-      </c>
-      <c r="D243" t="s">
+      <c r="B245" t="s">
+        <v>266</v>
+      </c>
+      <c r="C245" t="s">
+        <v>168</v>
+      </c>
+      <c r="D245" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A244" t="s">
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
         <v>178</v>
       </c>
-      <c r="B244" t="s">
-        <v>266</v>
-      </c>
-      <c r="C244" t="s">
-        <v>168</v>
-      </c>
-      <c r="D244" t="s">
+      <c r="B246" t="s">
+        <v>266</v>
+      </c>
+      <c r="C246" t="s">
+        <v>168</v>
+      </c>
+      <c r="D246" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A245" t="s">
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
         <v>180</v>
       </c>
-      <c r="B245" t="s">
-        <v>266</v>
-      </c>
-      <c r="C245" t="s">
-        <v>168</v>
-      </c>
-      <c r="D245" t="s">
+      <c r="B247" t="s">
+        <v>266</v>
+      </c>
+      <c r="C247" t="s">
+        <v>168</v>
+      </c>
+      <c r="D247" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A246" t="s">
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
         <v>182</v>
       </c>
-      <c r="B246" t="s">
-        <v>266</v>
-      </c>
-      <c r="C246" t="s">
-        <v>168</v>
-      </c>
-      <c r="D246" t="s">
+      <c r="B248" t="s">
+        <v>266</v>
+      </c>
+      <c r="C248" t="s">
+        <v>168</v>
+      </c>
+      <c r="D248" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A247" t="s">
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>184</v>
       </c>
-      <c r="B247" t="s">
-        <v>266</v>
-      </c>
-      <c r="C247" t="s">
-        <v>168</v>
-      </c>
-      <c r="D247" t="s">
+      <c r="B249" t="s">
+        <v>266</v>
+      </c>
+      <c r="C249" t="s">
+        <v>168</v>
+      </c>
+      <c r="D249" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
         <v>186</v>
       </c>
-      <c r="B248" t="s">
-        <v>266</v>
-      </c>
-      <c r="C248" t="s">
-        <v>168</v>
-      </c>
-      <c r="D248" t="s">
+      <c r="B250" t="s">
+        <v>266</v>
+      </c>
+      <c r="C250" t="s">
+        <v>168</v>
+      </c>
+      <c r="D250" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A249" t="s">
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
         <v>188</v>
       </c>
-      <c r="B249" t="s">
-        <v>266</v>
-      </c>
-      <c r="C249" t="s">
-        <v>168</v>
-      </c>
-      <c r="D249" t="s">
+      <c r="B251" t="s">
+        <v>266</v>
+      </c>
+      <c r="C251" t="s">
+        <v>168</v>
+      </c>
+      <c r="D251" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A250" t="s">
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
         <v>190</v>
       </c>
-      <c r="B250" t="s">
-        <v>266</v>
-      </c>
-      <c r="C250" t="s">
-        <v>168</v>
-      </c>
-      <c r="D250" t="s">
+      <c r="B252" t="s">
+        <v>266</v>
+      </c>
+      <c r="C252" t="s">
+        <v>168</v>
+      </c>
+      <c r="D252" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
         <v>192</v>
       </c>
-      <c r="B251" t="s">
-        <v>266</v>
-      </c>
-      <c r="C251" t="s">
-        <v>168</v>
-      </c>
-      <c r="D251" t="s">
+      <c r="B253" t="s">
+        <v>266</v>
+      </c>
+      <c r="C253" t="s">
+        <v>168</v>
+      </c>
+      <c r="D253" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A252" t="s">
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
         <v>170</v>
       </c>
-      <c r="B252" t="s">
-        <v>266</v>
-      </c>
-      <c r="C252" t="s">
-        <v>168</v>
-      </c>
-      <c r="D252" t="s">
+      <c r="B254" t="s">
+        <v>266</v>
+      </c>
+      <c r="C254" t="s">
+        <v>168</v>
+      </c>
+      <c r="D254" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A253" t="s">
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
         <v>284</v>
       </c>
-      <c r="B253" t="s">
-        <v>266</v>
-      </c>
-      <c r="C253" t="s">
-        <v>168</v>
-      </c>
-      <c r="D253" t="s">
+      <c r="B255" t="s">
+        <v>266</v>
+      </c>
+      <c r="C255" t="s">
+        <v>168</v>
+      </c>
+      <c r="D255" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
         <v>286</v>
       </c>
-      <c r="B254" t="s">
-        <v>266</v>
-      </c>
-      <c r="C254" t="s">
-        <v>168</v>
-      </c>
-      <c r="D254" t="s">
+      <c r="B256" t="s">
+        <v>266</v>
+      </c>
+      <c r="C256" t="s">
+        <v>168</v>
+      </c>
+      <c r="D256" t="s">
         <v>287</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>288</v>
-      </c>
-      <c r="B255" t="s">
-        <v>266</v>
-      </c>
-      <c r="C255" t="s">
-        <v>168</v>
-      </c>
-      <c r="D255" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>290</v>
-      </c>
-      <c r="B256" t="s">
-        <v>266</v>
-      </c>
-      <c r="C256" t="s">
-        <v>168</v>
-      </c>
-      <c r="D256" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B257" t="s">
         <v>266</v>
@@ -6318,12 +6333,12 @@
         <v>168</v>
       </c>
       <c r="D257" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B258" t="s">
         <v>266</v>
@@ -6332,12 +6347,12 @@
         <v>168</v>
       </c>
       <c r="D258" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B259" t="s">
         <v>266</v>
@@ -6346,12 +6361,12 @@
         <v>168</v>
       </c>
       <c r="D259" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B260" t="s">
         <v>266</v>
@@ -6360,12 +6375,12 @@
         <v>168</v>
       </c>
       <c r="D260" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B261" t="s">
         <v>266</v>
@@ -6374,12 +6389,12 @@
         <v>168</v>
       </c>
       <c r="D261" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B262" t="s">
         <v>266</v>
@@ -6388,12 +6403,12 @@
         <v>168</v>
       </c>
       <c r="D262" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B263" t="s">
         <v>266</v>
@@ -6402,12 +6417,12 @@
         <v>168</v>
       </c>
       <c r="D263" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B264" t="s">
         <v>266</v>
@@ -6416,12 +6431,12 @@
         <v>168</v>
       </c>
       <c r="D264" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B265" t="s">
         <v>266</v>
@@ -6430,12 +6445,12 @@
         <v>168</v>
       </c>
       <c r="D265" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B266" t="s">
         <v>266</v>
@@ -6444,12 +6459,12 @@
         <v>168</v>
       </c>
       <c r="D266" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B267" t="s">
         <v>266</v>
@@ -6458,12 +6473,12 @@
         <v>168</v>
       </c>
       <c r="D267" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B268" t="s">
         <v>266</v>
@@ -6472,12 +6487,12 @@
         <v>168</v>
       </c>
       <c r="D268" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B269" t="s">
         <v>266</v>
@@ -6486,12 +6501,12 @@
         <v>168</v>
       </c>
       <c r="D269" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B270" t="s">
         <v>266</v>
@@ -6500,12 +6515,12 @@
         <v>168</v>
       </c>
       <c r="D270" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B271" t="s">
         <v>266</v>
@@ -6514,12 +6529,12 @@
         <v>168</v>
       </c>
       <c r="D271" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B272" t="s">
         <v>266</v>
@@ -6528,12 +6543,12 @@
         <v>168</v>
       </c>
       <c r="D272" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B273" t="s">
         <v>266</v>
@@ -6542,12 +6557,12 @@
         <v>168</v>
       </c>
       <c r="D273" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B274" t="s">
         <v>266</v>
@@ -6556,12 +6571,12 @@
         <v>168</v>
       </c>
       <c r="D274" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B275" t="s">
         <v>266</v>
@@ -6570,12 +6585,12 @@
         <v>168</v>
       </c>
       <c r="D275" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B276" t="s">
         <v>266</v>
@@ -6584,12 +6599,12 @@
         <v>168</v>
       </c>
       <c r="D276" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B277" t="s">
         <v>266</v>
@@ -6598,12 +6613,12 @@
         <v>168</v>
       </c>
       <c r="D277" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B278" t="s">
         <v>266</v>
@@ -6612,12 +6627,12 @@
         <v>168</v>
       </c>
       <c r="D278" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B279" t="s">
         <v>266</v>
@@ -6626,12 +6641,12 @@
         <v>168</v>
       </c>
       <c r="D279" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B280" t="s">
         <v>266</v>
@@ -6640,12 +6655,12 @@
         <v>168</v>
       </c>
       <c r="D280" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B281" t="s">
         <v>266</v>
@@ -6654,12 +6669,12 @@
         <v>168</v>
       </c>
       <c r="D281" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>198</v>
+        <v>338</v>
       </c>
       <c r="B282" t="s">
         <v>266</v>
@@ -6668,12 +6683,12 @@
         <v>168</v>
       </c>
       <c r="D282" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>202</v>
+        <v>340</v>
       </c>
       <c r="B283" t="s">
         <v>266</v>
@@ -6682,12 +6697,12 @@
         <v>168</v>
       </c>
       <c r="D283" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="B284" t="s">
         <v>266</v>
@@ -6696,12 +6711,12 @@
         <v>168</v>
       </c>
       <c r="D284" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="B285" t="s">
         <v>266</v>
@@ -6710,12 +6725,12 @@
         <v>168</v>
       </c>
       <c r="D285" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="B286" t="s">
         <v>266</v>
@@ -6724,12 +6739,12 @@
         <v>168</v>
       </c>
       <c r="D286" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="B287" t="s">
         <v>266</v>
@@ -6738,12 +6753,12 @@
         <v>168</v>
       </c>
       <c r="D287" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="B288" t="s">
         <v>266</v>
@@ -6752,12 +6767,12 @@
         <v>168</v>
       </c>
       <c r="D288" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="B289" t="s">
         <v>266</v>
@@ -6766,12 +6781,12 @@
         <v>168</v>
       </c>
       <c r="D289" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B290" t="s">
         <v>266</v>
@@ -6780,12 +6795,12 @@
         <v>168</v>
       </c>
       <c r="D290" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B291" t="s">
         <v>266</v>
@@ -6794,12 +6809,12 @@
         <v>168</v>
       </c>
       <c r="D291" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="B292" t="s">
         <v>266</v>
@@ -6808,12 +6823,12 @@
         <v>168</v>
       </c>
       <c r="D292" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="B293" t="s">
         <v>266</v>
@@ -6822,12 +6837,12 @@
         <v>168</v>
       </c>
       <c r="D293" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="B294" t="s">
         <v>266</v>
@@ -6836,12 +6851,12 @@
         <v>168</v>
       </c>
       <c r="D294" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>355</v>
+        <v>222</v>
       </c>
       <c r="B295" t="s">
         <v>266</v>
@@ -6850,12 +6865,12 @@
         <v>168</v>
       </c>
       <c r="D295" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>357</v>
+        <v>200</v>
       </c>
       <c r="B296" t="s">
         <v>266</v>
@@ -6864,12 +6879,12 @@
         <v>168</v>
       </c>
       <c r="D296" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B297" t="s">
         <v>266</v>
@@ -6878,12 +6893,12 @@
         <v>168</v>
       </c>
       <c r="D297" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B298" t="s">
         <v>266</v>
@@ -6892,12 +6907,12 @@
         <v>168</v>
       </c>
       <c r="D298" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B299" t="s">
         <v>266</v>
@@ -6906,12 +6921,12 @@
         <v>168</v>
       </c>
       <c r="D299" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B300" t="s">
         <v>266</v>
@@ -6920,12 +6935,12 @@
         <v>168</v>
       </c>
       <c r="D300" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B301" t="s">
         <v>266</v>
@@ -6934,12 +6949,12 @@
         <v>168</v>
       </c>
       <c r="D301" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B302" t="s">
         <v>266</v>
@@ -6948,12 +6963,12 @@
         <v>168</v>
       </c>
       <c r="D302" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B303" t="s">
         <v>266</v>
@@ -6962,12 +6977,12 @@
         <v>168</v>
       </c>
       <c r="D303" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B304" t="s">
         <v>266</v>
@@ -6976,12 +6991,12 @@
         <v>168</v>
       </c>
       <c r="D304" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B305" t="s">
         <v>266</v>
@@ -6990,12 +7005,12 @@
         <v>168</v>
       </c>
       <c r="D305" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B306" t="s">
         <v>266</v>
@@ -7004,12 +7019,12 @@
         <v>168</v>
       </c>
       <c r="D306" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B307" t="s">
         <v>266</v>
@@ -7018,12 +7033,12 @@
         <v>168</v>
       </c>
       <c r="D307" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B308" t="s">
         <v>266</v>
@@ -7032,12 +7047,12 @@
         <v>168</v>
       </c>
       <c r="D308" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B309" t="s">
         <v>266</v>
@@ -7046,12 +7061,12 @@
         <v>168</v>
       </c>
       <c r="D309" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B310" t="s">
         <v>266</v>
@@ -7060,12 +7075,12 @@
         <v>168</v>
       </c>
       <c r="D310" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B311" t="s">
         <v>266</v>
@@ -7074,12 +7089,12 @@
         <v>168</v>
       </c>
       <c r="D311" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B312" t="s">
         <v>266</v>
@@ -7088,12 +7103,12 @@
         <v>168</v>
       </c>
       <c r="D312" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B313" t="s">
         <v>266</v>
@@ -7102,12 +7117,12 @@
         <v>168</v>
       </c>
       <c r="D313" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B314" t="s">
         <v>266</v>
@@ -7116,12 +7131,12 @@
         <v>168</v>
       </c>
       <c r="D314" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B315" t="s">
         <v>266</v>
@@ -7130,12 +7145,12 @@
         <v>168</v>
       </c>
       <c r="D315" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B316" t="s">
         <v>266</v>
@@ -7144,12 +7159,12 @@
         <v>168</v>
       </c>
       <c r="D316" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B317" t="s">
         <v>266</v>
@@ -7158,12 +7173,12 @@
         <v>168</v>
       </c>
       <c r="D317" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B318" t="s">
         <v>266</v>
@@ -7172,12 +7187,12 @@
         <v>168</v>
       </c>
       <c r="D318" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B319" t="s">
         <v>266</v>
@@ -7186,12 +7201,12 @@
         <v>168</v>
       </c>
       <c r="D319" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B320" t="s">
         <v>266</v>
@@ -7200,12 +7215,12 @@
         <v>168</v>
       </c>
       <c r="D320" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B321" t="s">
         <v>266</v>
@@ -7214,12 +7229,12 @@
         <v>168</v>
       </c>
       <c r="D321" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B322" t="s">
         <v>266</v>
@@ -7228,12 +7243,12 @@
         <v>168</v>
       </c>
       <c r="D322" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B323" t="s">
         <v>266</v>
@@ -7242,68 +7257,68 @@
         <v>168</v>
       </c>
       <c r="D323" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>245</v>
+        <v>409</v>
       </c>
       <c r="B324" t="s">
         <v>266</v>
       </c>
       <c r="C324" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D324" t="s">
-        <v>246</v>
+        <v>410</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>247</v>
+        <v>411</v>
       </c>
       <c r="B325" t="s">
         <v>266</v>
       </c>
       <c r="C325" t="s">
-        <v>229</v>
+        <v>168</v>
       </c>
       <c r="D325" t="s">
-        <v>248</v>
+        <v>412</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>413</v>
+        <v>245</v>
       </c>
       <c r="B326" t="s">
         <v>266</v>
       </c>
       <c r="C326" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="D326" t="s">
-        <v>414</v>
+        <v>246</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>415</v>
+        <v>247</v>
       </c>
       <c r="B327" t="s">
         <v>266</v>
       </c>
       <c r="C327" t="s">
-        <v>7</v>
+        <v>229</v>
       </c>
       <c r="D327" t="s">
-        <v>416</v>
+        <v>248</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B328" t="s">
         <v>266</v>
@@ -7312,12 +7327,12 @@
         <v>7</v>
       </c>
       <c r="D328" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B329" t="s">
         <v>266</v>
@@ -7326,12 +7341,12 @@
         <v>7</v>
       </c>
       <c r="D329" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B330" t="s">
         <v>266</v>
@@ -7340,12 +7355,12 @@
         <v>7</v>
       </c>
       <c r="D330" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B331" t="s">
         <v>266</v>
@@ -7354,12 +7369,12 @@
         <v>7</v>
       </c>
       <c r="D331" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B332" t="s">
         <v>266</v>
@@ -7368,12 +7383,12 @@
         <v>7</v>
       </c>
       <c r="D332" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B333" t="s">
         <v>266</v>
@@ -7382,12 +7397,12 @@
         <v>7</v>
       </c>
       <c r="D333" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B334" t="s">
         <v>266</v>
@@ -7396,12 +7411,12 @@
         <v>7</v>
       </c>
       <c r="D334" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B335" t="s">
         <v>266</v>
@@ -7410,12 +7425,12 @@
         <v>7</v>
       </c>
       <c r="D335" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B336" t="s">
         <v>266</v>
@@ -7424,12 +7439,12 @@
         <v>7</v>
       </c>
       <c r="D336" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B337" t="s">
         <v>266</v>
@@ -7438,25 +7453,53 @@
         <v>7</v>
       </c>
       <c r="D337" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
+        <v>433</v>
+      </c>
+      <c r="B338" t="s">
+        <v>266</v>
+      </c>
+      <c r="C338" t="s">
+        <v>7</v>
+      </c>
+      <c r="D338" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A339" t="s">
+        <v>435</v>
+      </c>
+      <c r="B339" t="s">
+        <v>266</v>
+      </c>
+      <c r="C339" t="s">
+        <v>7</v>
+      </c>
+      <c r="D339" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A340" t="s">
         <v>437</v>
       </c>
-      <c r="B338" t="s">
-        <v>266</v>
-      </c>
-      <c r="C338" t="s">
-        <v>7</v>
-      </c>
-      <c r="D338" t="s">
+      <c r="B340" t="s">
+        <v>266</v>
+      </c>
+      <c r="C340" t="s">
+        <v>7</v>
+      </c>
+      <c r="D340" t="s">
         <v>438</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F338" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F340" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/data-raw/xlsx/tabla_etiquetas.xlsx
+++ b/data-raw/xlsx/tabla_etiquetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fernando_gallegos\Proyectos\odsa.eusilc\data-raw\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4517D1AB-8FB8-4F8F-8BC3-487FD50F3B8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFA112ED-33CC-4E64-B824-B633F54BD296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11760" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$349</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Hoja1!$A$1:$F$352</definedName>
   </definedNames>
   <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1585" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="466">
   <si>
     <t>variable</t>
   </si>
@@ -1417,6 +1417,15 @@
   </si>
   <si>
     <t>Cantidad de años presentes del grupo de rotación</t>
+  </si>
+  <si>
+    <t>hi08a</t>
+  </si>
+  <si>
+    <t>hi08b</t>
+  </si>
+  <si>
+    <t>hi08c</t>
   </si>
 </sst>
 </file>
@@ -1656,7 +1665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F349"/>
+  <dimension ref="A1:F352"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -6280,63 +6289,63 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>291</v>
+        <v>463</v>
       </c>
       <c r="B250" t="s">
         <v>285</v>
       </c>
       <c r="C250" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="D250" t="s">
-        <v>292</v>
+        <v>35</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>186</v>
+        <v>464</v>
       </c>
       <c r="B251" t="s">
         <v>285</v>
       </c>
       <c r="C251" t="s">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="D251" t="s">
-        <v>293</v>
+        <v>37</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>191</v>
+        <v>465</v>
       </c>
       <c r="B252" t="s">
         <v>285</v>
       </c>
       <c r="C252" t="s">
-        <v>187</v>
+        <v>8</v>
       </c>
       <c r="D252" t="s">
-        <v>294</v>
+        <v>462</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>193</v>
+        <v>291</v>
       </c>
       <c r="B253" t="s">
         <v>285</v>
       </c>
       <c r="C253" t="s">
-        <v>187</v>
+        <v>39</v>
       </c>
       <c r="D253" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B254" t="s">
         <v>285</v>
@@ -6345,12 +6354,12 @@
         <v>187</v>
       </c>
       <c r="D254" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="B255" t="s">
         <v>285</v>
@@ -6359,12 +6368,12 @@
         <v>187</v>
       </c>
       <c r="D255" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="B256" t="s">
         <v>285</v>
@@ -6373,12 +6382,12 @@
         <v>187</v>
       </c>
       <c r="D256" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B257" t="s">
         <v>285</v>
@@ -6387,12 +6396,12 @@
         <v>187</v>
       </c>
       <c r="D257" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="B258" t="s">
         <v>285</v>
@@ -6401,12 +6410,12 @@
         <v>187</v>
       </c>
       <c r="D258" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="B259" t="s">
         <v>285</v>
@@ -6415,12 +6424,12 @@
         <v>187</v>
       </c>
       <c r="D259" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="B260" t="s">
         <v>285</v>
@@ -6429,12 +6438,12 @@
         <v>187</v>
       </c>
       <c r="D260" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B261" t="s">
         <v>285</v>
@@ -6443,12 +6452,12 @@
         <v>187</v>
       </c>
       <c r="D261" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B262" t="s">
         <v>285</v>
@@ -6457,12 +6466,12 @@
         <v>187</v>
       </c>
       <c r="D262" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B263" t="s">
         <v>285</v>
@@ -6471,12 +6480,12 @@
         <v>187</v>
       </c>
       <c r="D263" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>306</v>
+        <v>209</v>
       </c>
       <c r="B264" t="s">
         <v>285</v>
@@ -6485,12 +6494,12 @@
         <v>187</v>
       </c>
       <c r="D264" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>308</v>
+        <v>211</v>
       </c>
       <c r="B265" t="s">
         <v>285</v>
@@ -6499,12 +6508,12 @@
         <v>187</v>
       </c>
       <c r="D265" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>310</v>
+        <v>189</v>
       </c>
       <c r="B266" t="s">
         <v>285</v>
@@ -6513,12 +6522,12 @@
         <v>187</v>
       </c>
       <c r="D266" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B267" t="s">
         <v>285</v>
@@ -6527,12 +6536,12 @@
         <v>187</v>
       </c>
       <c r="D267" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B268" t="s">
         <v>285</v>
@@ -6541,12 +6550,12 @@
         <v>187</v>
       </c>
       <c r="D268" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B269" t="s">
         <v>285</v>
@@ -6555,12 +6564,12 @@
         <v>187</v>
       </c>
       <c r="D269" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B270" t="s">
         <v>285</v>
@@ -6569,12 +6578,12 @@
         <v>187</v>
       </c>
       <c r="D270" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B271" t="s">
         <v>285</v>
@@ -6583,12 +6592,12 @@
         <v>187</v>
       </c>
       <c r="D271" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B272" t="s">
         <v>285</v>
@@ -6597,12 +6606,12 @@
         <v>187</v>
       </c>
       <c r="D272" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B273" t="s">
         <v>285</v>
@@ -6611,12 +6620,12 @@
         <v>187</v>
       </c>
       <c r="D273" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B274" t="s">
         <v>285</v>
@@ -6625,12 +6634,12 @@
         <v>187</v>
       </c>
       <c r="D274" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="B275" t="s">
         <v>285</v>
@@ -6639,12 +6648,12 @@
         <v>187</v>
       </c>
       <c r="D275" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B276" t="s">
         <v>285</v>
@@ -6653,12 +6662,12 @@
         <v>187</v>
       </c>
       <c r="D276" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B277" t="s">
         <v>285</v>
@@ -6667,12 +6676,12 @@
         <v>187</v>
       </c>
       <c r="D277" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B278" t="s">
         <v>285</v>
@@ -6681,12 +6690,12 @@
         <v>187</v>
       </c>
       <c r="D278" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="B279" t="s">
         <v>285</v>
@@ -6695,12 +6704,12 @@
         <v>187</v>
       </c>
       <c r="D279" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B280" t="s">
         <v>285</v>
@@ -6709,12 +6718,12 @@
         <v>187</v>
       </c>
       <c r="D280" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="B281" t="s">
         <v>285</v>
@@ -6723,12 +6732,12 @@
         <v>187</v>
       </c>
       <c r="D281" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B282" t="s">
         <v>285</v>
@@ -6737,12 +6746,12 @@
         <v>187</v>
       </c>
       <c r="D282" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B283" t="s">
         <v>285</v>
@@ -6751,12 +6760,12 @@
         <v>187</v>
       </c>
       <c r="D283" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="B284" t="s">
         <v>285</v>
@@ -6765,12 +6774,12 @@
         <v>187</v>
       </c>
       <c r="D284" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B285" t="s">
         <v>285</v>
@@ -6779,12 +6788,12 @@
         <v>187</v>
       </c>
       <c r="D285" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B286" t="s">
         <v>285</v>
@@ -6793,12 +6802,12 @@
         <v>187</v>
       </c>
       <c r="D286" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="B287" t="s">
         <v>285</v>
@@ -6807,12 +6816,12 @@
         <v>187</v>
       </c>
       <c r="D287" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="B288" t="s">
         <v>285</v>
@@ -6821,12 +6830,12 @@
         <v>187</v>
       </c>
       <c r="D288" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="B289" t="s">
         <v>285</v>
@@ -6835,12 +6844,12 @@
         <v>187</v>
       </c>
       <c r="D289" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B290" t="s">
         <v>285</v>
@@ -6849,12 +6858,12 @@
         <v>187</v>
       </c>
       <c r="D290" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="B291" t="s">
         <v>285</v>
@@ -6863,12 +6872,12 @@
         <v>187</v>
       </c>
       <c r="D291" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="B292" t="s">
         <v>285</v>
@@ -6877,12 +6886,12 @@
         <v>187</v>
       </c>
       <c r="D292" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>217</v>
+        <v>358</v>
       </c>
       <c r="B293" t="s">
         <v>285</v>
@@ -6891,12 +6900,12 @@
         <v>187</v>
       </c>
       <c r="D293" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>221</v>
+        <v>360</v>
       </c>
       <c r="B294" t="s">
         <v>285</v>
@@ -6905,12 +6914,12 @@
         <v>187</v>
       </c>
       <c r="D294" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>223</v>
+        <v>362</v>
       </c>
       <c r="B295" t="s">
         <v>285</v>
@@ -6919,12 +6928,12 @@
         <v>187</v>
       </c>
       <c r="D295" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B296" t="s">
         <v>285</v>
@@ -6933,12 +6942,12 @@
         <v>187</v>
       </c>
       <c r="D296" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="B297" t="s">
         <v>285</v>
@@ -6947,12 +6956,12 @@
         <v>187</v>
       </c>
       <c r="D297" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B298" t="s">
         <v>285</v>
@@ -6961,12 +6970,12 @@
         <v>187</v>
       </c>
       <c r="D298" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="B299" t="s">
         <v>285</v>
@@ -6975,12 +6984,12 @@
         <v>187</v>
       </c>
       <c r="D299" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B300" t="s">
         <v>285</v>
@@ -6989,12 +6998,12 @@
         <v>187</v>
       </c>
       <c r="D300" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="B301" t="s">
         <v>285</v>
@@ -7003,12 +7012,12 @@
         <v>187</v>
       </c>
       <c r="D301" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B302" t="s">
         <v>285</v>
@@ -7017,12 +7026,12 @@
         <v>187</v>
       </c>
       <c r="D302" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="B303" t="s">
         <v>285</v>
@@ -7031,12 +7040,12 @@
         <v>187</v>
       </c>
       <c r="D303" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="B304" t="s">
         <v>285</v>
@@ -7045,12 +7054,12 @@
         <v>187</v>
       </c>
       <c r="D304" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B305" t="s">
         <v>285</v>
@@ -7059,12 +7068,12 @@
         <v>187</v>
       </c>
       <c r="D305" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>377</v>
+        <v>239</v>
       </c>
       <c r="B306" t="s">
         <v>285</v>
@@ -7073,12 +7082,12 @@
         <v>187</v>
       </c>
       <c r="D306" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>379</v>
+        <v>241</v>
       </c>
       <c r="B307" t="s">
         <v>285</v>
@@ -7087,12 +7096,12 @@
         <v>187</v>
       </c>
       <c r="D307" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>381</v>
+        <v>219</v>
       </c>
       <c r="B308" t="s">
         <v>285</v>
@@ -7101,12 +7110,12 @@
         <v>187</v>
       </c>
       <c r="D308" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="B309" t="s">
         <v>285</v>
@@ -7115,12 +7124,12 @@
         <v>187</v>
       </c>
       <c r="D309" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B310" t="s">
         <v>285</v>
@@ -7129,12 +7138,12 @@
         <v>187</v>
       </c>
       <c r="D310" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B311" t="s">
         <v>285</v>
@@ -7143,12 +7152,12 @@
         <v>187</v>
       </c>
       <c r="D311" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B312" t="s">
         <v>285</v>
@@ -7157,12 +7166,12 @@
         <v>187</v>
       </c>
       <c r="D312" t="s">
-        <v>390</v>
+        <v>384</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B313" t="s">
         <v>285</v>
@@ -7171,12 +7180,12 @@
         <v>187</v>
       </c>
       <c r="D313" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B314" t="s">
         <v>285</v>
@@ -7185,12 +7194,12 @@
         <v>187</v>
       </c>
       <c r="D314" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="B315" t="s">
         <v>285</v>
@@ -7199,12 +7208,12 @@
         <v>187</v>
       </c>
       <c r="D315" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B316" t="s">
         <v>285</v>
@@ -7213,12 +7222,12 @@
         <v>187</v>
       </c>
       <c r="D316" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="B317" t="s">
         <v>285</v>
@@ -7227,12 +7236,12 @@
         <v>187</v>
       </c>
       <c r="D317" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B318" t="s">
         <v>285</v>
@@ -7241,12 +7250,12 @@
         <v>187</v>
       </c>
       <c r="D318" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B319" t="s">
         <v>285</v>
@@ -7255,12 +7264,12 @@
         <v>187</v>
       </c>
       <c r="D319" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B320" t="s">
         <v>285</v>
@@ -7269,12 +7278,12 @@
         <v>187</v>
       </c>
       <c r="D320" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="B321" t="s">
         <v>285</v>
@@ -7283,12 +7292,12 @@
         <v>187</v>
       </c>
       <c r="D321" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="B322" t="s">
         <v>285</v>
@@ -7297,12 +7306,12 @@
         <v>187</v>
       </c>
       <c r="D322" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="B323" t="s">
         <v>285</v>
@@ -7311,12 +7320,12 @@
         <v>187</v>
       </c>
       <c r="D323" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B324" t="s">
         <v>285</v>
@@ -7325,12 +7334,12 @@
         <v>187</v>
       </c>
       <c r="D324" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B325" t="s">
         <v>285</v>
@@ -7339,12 +7348,12 @@
         <v>187</v>
       </c>
       <c r="D325" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="B326" t="s">
         <v>285</v>
@@ -7353,12 +7362,12 @@
         <v>187</v>
       </c>
       <c r="D326" t="s">
-        <v>418</v>
+        <v>412</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="B327" t="s">
         <v>285</v>
@@ -7367,12 +7376,12 @@
         <v>187</v>
       </c>
       <c r="D327" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B328" t="s">
         <v>285</v>
@@ -7381,12 +7390,12 @@
         <v>187</v>
       </c>
       <c r="D328" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B329" t="s">
         <v>285</v>
@@ -7395,12 +7404,12 @@
         <v>187</v>
       </c>
       <c r="D329" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B330" t="s">
         <v>285</v>
@@ -7409,12 +7418,12 @@
         <v>187</v>
       </c>
       <c r="D330" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B331" t="s">
         <v>285</v>
@@ -7423,12 +7432,12 @@
         <v>187</v>
       </c>
       <c r="D331" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
       <c r="B332" t="s">
         <v>285</v>
@@ -7437,12 +7446,12 @@
         <v>187</v>
       </c>
       <c r="D332" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B333" t="s">
         <v>285</v>
@@ -7451,12 +7460,12 @@
         <v>187</v>
       </c>
       <c r="D333" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
       <c r="B334" t="s">
         <v>285</v>
@@ -7465,82 +7474,82 @@
         <v>187</v>
       </c>
       <c r="D334" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>264</v>
+        <v>429</v>
       </c>
       <c r="B335" t="s">
         <v>285</v>
       </c>
       <c r="C335" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="D335" t="s">
-        <v>265</v>
+        <v>430</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>266</v>
+        <v>431</v>
       </c>
       <c r="B336" t="s">
         <v>285</v>
       </c>
       <c r="C336" t="s">
-        <v>248</v>
+        <v>187</v>
       </c>
       <c r="D336" t="s">
-        <v>267</v>
+        <v>432</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B337" t="s">
         <v>285</v>
       </c>
       <c r="C337" t="s">
-        <v>7</v>
+        <v>187</v>
       </c>
       <c r="D337" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="B338" t="s">
         <v>285</v>
       </c>
       <c r="C338" t="s">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="D338" t="s">
-        <v>438</v>
+        <v>265</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>439</v>
+        <v>266</v>
       </c>
       <c r="B339" t="s">
         <v>285</v>
       </c>
       <c r="C339" t="s">
-        <v>7</v>
+        <v>248</v>
       </c>
       <c r="D339" t="s">
-        <v>440</v>
+        <v>267</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="B340" t="s">
         <v>285</v>
@@ -7549,12 +7558,12 @@
         <v>7</v>
       </c>
       <c r="D340" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B341" t="s">
         <v>285</v>
@@ -7563,12 +7572,12 @@
         <v>7</v>
       </c>
       <c r="D341" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
       <c r="B342" t="s">
         <v>285</v>
@@ -7577,12 +7586,12 @@
         <v>7</v>
       </c>
       <c r="D342" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
       <c r="B343" t="s">
         <v>285</v>
@@ -7591,12 +7600,12 @@
         <v>7</v>
       </c>
       <c r="D343" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="B344" t="s">
         <v>285</v>
@@ -7605,12 +7614,12 @@
         <v>7</v>
       </c>
       <c r="D344" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="B345" t="s">
         <v>285</v>
@@ -7619,12 +7628,12 @@
         <v>7</v>
       </c>
       <c r="D345" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="B346" t="s">
         <v>285</v>
@@ -7633,12 +7642,12 @@
         <v>7</v>
       </c>
       <c r="D346" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="B347" t="s">
         <v>285</v>
@@ -7647,12 +7656,12 @@
         <v>7</v>
       </c>
       <c r="D347" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="B348" t="s">
         <v>285</v>
@@ -7661,25 +7670,67 @@
         <v>7</v>
       </c>
       <c r="D348" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>453</v>
+      </c>
+      <c r="B349" t="s">
+        <v>285</v>
+      </c>
+      <c r="C349" t="s">
+        <v>7</v>
+      </c>
+      <c r="D349" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A350" t="s">
+        <v>455</v>
+      </c>
+      <c r="B350" t="s">
+        <v>285</v>
+      </c>
+      <c r="C350" t="s">
+        <v>7</v>
+      </c>
+      <c r="D350" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A351" t="s">
+        <v>457</v>
+      </c>
+      <c r="B351" t="s">
+        <v>285</v>
+      </c>
+      <c r="C351" t="s">
+        <v>7</v>
+      </c>
+      <c r="D351" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A352" t="s">
         <v>459</v>
       </c>
-      <c r="B349" t="s">
-        <v>285</v>
-      </c>
-      <c r="C349" t="s">
-        <v>7</v>
-      </c>
-      <c r="D349" t="s">
+      <c r="B352" t="s">
+        <v>285</v>
+      </c>
+      <c r="C352" t="s">
+        <v>7</v>
+      </c>
+      <c r="D352" t="s">
         <v>460</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F349" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:F352" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
